--- a/forms/trg/Formulir_TRG_ecofor.xlsx
+++ b/forms/trg/Formulir_TRG_ecofor.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B24)</f>
+        <f>COUNTA(Anggota!B5:B25)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F24)</f>
+        <f>COUNTA(Anggota!F5:F25)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,37 +913,37 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Anugrahandini Nasir, S.Hut, M.Si</t>
+          <t>Prof. Dr. Ir. Amran Achmad, M.Sc.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Makassar Islamic University</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="n"/>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Forest Ecology</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0009-0000-4357-6438</t>
+          <t>0000-0001-5336-5028</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6881727</t>
+          <t>5982188</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57221788301</t>
+          <t>55773790500</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -958,17 +958,17 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Arida Fauziyah, S.Si., M.Sc.</t>
+          <t>Anugrahandini Nasir, S.Hut, M.Si</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Makassar Islamic University</t>
         </is>
       </c>
       <c r="E6" s="11" t="n"/>
@@ -978,17 +978,17 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-6755-6685</t>
+          <t>0009-0000-4357-6438</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6833139</t>
+          <t>6881727</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57210997226</t>
+          <t>57221788301</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Asrianny, S.Hut., M.Si.</t>
+          <t>Arida Fauziyah, S.Si., M.Sc.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1023,17 +1023,17 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-2733-9990</t>
+          <t>0000-0001-6755-6685</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6742781</t>
+          <t>6833139</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57218363864</t>
+          <t>57210997226</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1048,17 +1048,17 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Mohd Hafiz Hanafiah</t>
+          <t>Dr. Asrianny, S.Hut., M.Si.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Universiti Teknologi MARA (UiTM)</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E8" s="11" t="n"/>
@@ -1068,13 +1068,17 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-3378-7300</t>
-        </is>
-      </c>
-      <c r="K8" s="12" t="n"/>
+          <t>0000-0002-2733-9990</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>6742781</t>
+        </is>
+      </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>55371668100</t>
+          <t>57218363864</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1089,27 +1093,35 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Fandawa Saputra, S.Hut., M.Si</t>
+          <t>Prof. Dr. Mohd Hafiz Hanafiah</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>Researchers and practitioners in ecotourism</t>
-        </is>
-      </c>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Universiti Teknologi MARA (UiTM)</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="n"/>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-3378-7300</t>
+        </is>
+      </c>
       <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>55371668100</t>
+        </is>
+      </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1122,20 +1134,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>St. Nurfadilla Kasim</t>
+          <t>Fandawa Saputra, S.Hut., M.Si</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Researchers and practitioners in ecotourism</t>
+        </is>
+      </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
@@ -1155,12 +1167,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Nur Fajriani</t>
+          <t>St. Nurfadilla Kasim</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1188,12 +1200,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Hanjar Mulya</t>
+          <t>Nur Fajriani</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1206,17 +1218,9 @@
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>0009-0000-5289-5246</t>
-        </is>
-      </c>
+      <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>57245551500</t>
-        </is>
-      </c>
+      <c r="L12" s="12" t="n"/>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1227,18 +1231,46 @@
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="11" t="n"/>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Hanjar Mulya</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>The Ecotourism and Forest Biodiversity Research Group (ECOFOR) is dedicated to advancing sustainable ecotourism while conserving forest biodiversity. Through research, innovation, and collaboration, ECOFOR empowers local communities, builds strong networks, and provides reliable data and policy recommendations. Our mission is to balance conservation with development, fostering young researchers and shaping best practices for a sustainable future.</t>
+        </is>
+      </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>0009-0000-5289-5246</t>
+        </is>
+      </c>
       <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
-      <c r="M13" s="12" t="n"/>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>57245551500</t>
+        </is>
+      </c>
+      <c r="M13" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1427,15 +1459,32 @@
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="12" t="n"/>
     </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
